--- a/writable/exports/analytics_report.xlsx
+++ b/writable/exports/analytics_report.xlsx
@@ -385,7 +385,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>31.85</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -393,7 +393,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>31.85</v>
+        <v>47.07</v>
       </c>
     </row>
     <row r="4" spans="1:2">
